--- a/output/广义投诉流量202605_test_5_classified.xlsx
+++ b/output/广义投诉流量202605_test_5_classified.xlsx
@@ -495,12 +495,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>费用争议</t>
+          <t>流量问题</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>流量超套扣费</t>
+          <t>流量提醒不到位</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>客户对流量扣费有疑问，经查证后确认扣费无误且有提醒</t>
+          <t>客户投诉因未及时收到流量超套提醒而被扣费，要求退还超额费用</t>
         </is>
       </c>
     </row>
@@ -541,12 +541,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>费用争议</t>
+          <t>流量问题</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>流量超套扣费</t>
+          <t>流量提醒不到位</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>客户对流量扣费有疑问，经查证扣费无误且有提醒，属于流量超套扣费问题</t>
+          <t>客户投诉流量用尽没有短信提醒，导致高消费，且查证情况中提到有提醒但客户认为不及时</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>费用争议</t>
+          <t>流量问题</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>客户反馈流量超出问题，且经核实流量超出按套餐外计费，属于费用争议中的流量超套扣费</t>
+          <t>客户对超流量扣费不满，经核实扣费无误，但联系不上客户进一步处理</t>
         </is>
       </c>
     </row>
@@ -643,22 +643,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>费用争议</t>
+          <t>流量问题</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>账单异常</t>
+          <t>流量提醒不到位</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>客户对费用有疑问，经过解释和特殊申请返还费用后接受，属于费用争议</t>
+          <t>客户投诉未收到流量使用提醒，导致扣费后才通知。</t>
         </is>
       </c>
     </row>
@@ -695,22 +695,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>费用争议</t>
+          <t>流量问题</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>流量超套扣费</t>
+          <t>流量提醒不到位</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>客户对账单中的流量扣费有疑问，尽管查证无误，仍属于费用争议</t>
+          <t>客户投诉未经同意超额扣费且提醒无效，但查证无超流量记录，属于流量提醒争议</t>
         </is>
       </c>
     </row>

--- a/output/广义投诉流量202605_test_5_classified.xlsx
+++ b/output/广义投诉流量202605_test_5_classified.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,25 +439,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>投诉内容</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>归档意见(前200字)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>一级分类</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>二级分类</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>置信度</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>分类理由</t>
         </is>
@@ -483,6 +488,12 @@
         </is>
       </c>
       <c r="E2" t="inlineStr">
+        <is>
+          <t>投诉诉求：补偿争议金额；
+故障描述：移动短信没有及时通知我超出流量就扣我的话费，无缝衔接，即使是流量用完了，也不及时通知我。我以前就有要求到时候你们运营商在我用完流量的情况下，及时断网或你们要及时通知或者断网，很明显你们这次并没有做，反而是扣完的话费，等我发现的时候，切换网络，你们才发短信通知我，这是你们的过错，我要求很简单，要求全额退还我超出我的流量话费，不然就工信部投诉，我会坚持保护我的权益，</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>【问题概述】客户反映（流量扣费  ）问题。
 【查证情况】经查：本月产生流量费用30
@@ -493,24 +504,24 @@
 【联系客户时间及情况】5月13号电话联系本机根据查证结果解释，多次联系客户，客户未接听，结单</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>流量问题</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>流量提醒不到位</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>客户投诉因未及时收到流量超套提醒而被扣费，要求退还超额费用</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>客户投诉因未及时收到流量使用提醒导致超套扣费，查证结果也提到提醒问题</t>
         </is>
       </c>
     </row>
@@ -535,28 +546,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>投诉诉求：补偿争议金额；
+故障描述：流量日包用尽没有短信提醒，APP内有延迟也不准确，误导消费者高消费，而且不是第一次这样，必要情况下就到消费者热线投诉你们了</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>【问题概述】客户反映（流量扣费 ）问题。
 【查证情况】查证用户使用8元自由选套餐（100MB流量）  档，5月超流量78.45元，2026/05/12 22:55:05已退58.41元，有短信和IVR提醒，核实以上数据扣费不存在异常，计费无误,且流量不足和用完已下发短信提醒。建议客户使用上网如有WIFI时最好关闭数据网络，避免WIFI信号弱时自动切换至4G，并推荐关闭手机自动更新软件的设置，流量数</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>流量问题</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>流量提醒不到位</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>客户投诉流量用尽没有短信提醒，导致高消费，且查证情况中提到有提醒但客户认为不及时</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>客户投诉流量用尽没有短信提醒，且APP内显示延迟，导致高消费</t>
         </is>
       </c>
     </row>
@@ -580,6 +597,12 @@
         </is>
       </c>
       <c r="E4" t="inlineStr">
+        <is>
+          <t>#同步要素#是否119+融宽客户:是#同步要素#
+客户对超流量扣费不满，超出退费权限，请跟进。谢谢！提到12315、消费者热线，有升级意向</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>【问题概述】客户反馈流量超出的问题
 【查证情况】经核实客户使用199元全家享套餐（2024）  超出流量按5元1GB，15元后3元1GB计算，联系不上客户，无法进一步处理
@@ -589,24 +612,24 @@
 【联系客户情况】：在2026年5月13号时间联系（  13480526461）号码处理，客户均未接听，如客户来电请前台解释：。短信复：尊敬的客户：您向1008</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>流量问题</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>流量超套扣费</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>客户对超流量扣费不满，经核实扣费无误，但联系不上客户进一步处理</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>客户对超出套餐的流量扣费表示不满，且已核实扣费规则</t>
         </is>
       </c>
     </row>
@@ -630,6 +653,12 @@
         </is>
       </c>
       <c r="E5" t="inlineStr">
+        <is>
+          <t>投诉诉求：补偿争议金额；
+故障描述：流量没有了，为什么不通知？而是扣费了才通知？</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">问题概述】反馈流量超出费用的问题
 【查证情况】联系客户解释清楚属于正常使用，我司有正常下发信息提醒，客户意见大，本次特殊申请15.51元返还，下不为例，客户接受。
@@ -641,24 +670,24 @@
 </t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>流量问题</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>流量提醒不到位</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>客户投诉未收到流量使用提醒，导致扣费后才通知。</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>客户投诉流量扣费未提前通知，查证后确认有提醒但客户不认可</t>
         </is>
       </c>
     </row>
@@ -682,6 +711,12 @@
         </is>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>投诉诉求：补偿争议金额；
+故障描述：运营商未经本人同意私自超额扣流量话费，无效提醒、无本人授权</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>【问题概述】客户反映（ 账单流量扣费 ）问题。
 【查证情况】查证客户套餐是（79元套餐），今年内并无任何超流量扣费记录。
@@ -693,24 +728,24 @@
 【联系客户时间及情况】2026-05-12电话联系客户，有结合查证的情况和客户解释，今年无任何流量扣费，然后 提醒客户下个月更改了8元套餐，超出流量扣费比较贵，建议客户下个月开</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>流量问题</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>流量提醒不到位</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>客户投诉未经同意超额扣费且提醒无效，但查证无超流量记录，属于流量提醒争议</t>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>客户投诉未经同意超额扣费且提醒无效，但查证无超流量记录，主要问题是提醒不到位</t>
         </is>
       </c>
     </row>
